--- a/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D1EB1B-B45C-4149-AEE2-7B3180C9E8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36CF479-C585-4935-8ED7-863C73F71055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc." sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
   <si>
     <t>attribute</t>
   </si>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>*_hydro_ps*</t>
+  </si>
+  <si>
+    <t>ncap_drate</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
   </si>
 </sst>
 </file>
@@ -839,6 +845,17 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15">
+        <v>0.1</v>
+      </c>
+    </row>
     <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
         <v>17</v>

--- a/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36CF479-C585-4935-8ED7-863C73F71055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BBC20C-3030-43E2-998E-4E0277B02BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="60">
   <si>
     <t>attribute</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>coal</t>
   </si>
 </sst>
 </file>
@@ -623,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982CB9B3-DA63-443B-9AA5-BEE16CBC2D59}">
-  <dimension ref="B3:L25"/>
+  <dimension ref="B3:L27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
@@ -856,6 +859,20 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16">
+        <v>0.15</v>
+      </c>
+    </row>
     <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
         <v>17</v>
@@ -928,6 +945,34 @@
         <v>51</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>52</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/BY_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BBC20C-3030-43E2-998E-4E0277B02BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D696140F-E4F4-4F59-9EDD-DD4A5F7316F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
   <si>
     <t>attribute</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>coal</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>en*</t>
   </si>
 </sst>
 </file>
@@ -861,7 +867,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -869,8 +875,11 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
       <c r="H16">
-        <v>0.15</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
